--- a/knowledge/Koenig_VoiceBot_FAQ_Master.xlsx
+++ b/knowledge/Koenig_VoiceBot_FAQ_Master.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7634,6 +7634,444 @@
       <c r="K127" t="inlineStr">
         <is>
           <t>Type your gross annual salary into Ask Strides along with the word 'tax'. Examples that work: 'tax on 19 lakh', 'My salary is 25 lakh, what is tax?', 'tax on 1500000 with 80C 150000 and HRA 60000'. Strides will compute your liability under both regimes and tell you which one saves more. For your exact pay-slip liability please contact the Tax team at tax@koenig-solutions.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>How can I save tax?</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>save my tax; save my taxes; reduce my tax; how to reduce tax; tax planning; tax saving tips; how to minimise tax</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>save, reduce, minimise, planning, deduction, investment</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Here is how Koenig employees can save tax for FY 2026-27:
+**Step 1 — Choose the right regime.** Use the in-app **Tax Calculator** (Start Here → 🧮 Tax Calculator) to compare your liability under both regimes. As a rough rule of thumb: if your total deductions are below about ₹4 lakh, the **New Regime** usually saves more; if you fully use 80C + 80D + HRA + home-loan interest, the **Old Regime** often wins.
+**Step 2 — Under the Old Regime**, the main levers are: Section 80C up to ₹1,50,000 (PF, PPF, ELSS, LIC, tuition fees, home-loan principal); Section 80CCD(1B) additional ₹50,000 in NPS; Section 80D up to ₹1,00,000 (health insurance for you and senior-citizen parents); Section 24(b) up to ₹2,00,000 (self-occupied home-loan interest); HRA exemption (rent receipts + landlord PAN if rent &gt; ₹1L/year); Section 80E (full education-loan interest, no upper cap).
+**Step 3 — Under both regimes**, two Koenig-specific perks remain: **Meal Passes / Sodexo** (₹1,05,600 tax-free per year) and **Employer NPS 80CCD(2)** (employer contribution, no cap on employee's side).
+**Step 4 — Declare your investments** to the Tax team at tax@koenig-solutions.com so TDS is computed correctly through the year.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Here is how Koenig employees can save tax for FY 2026-27:
+**Step 1 — Choose the right regime.** Use the in-app **Tax Calculator** (Start Here → 🧮 Tax Calculator) to compare your liability under both regimes. As a rough rule of thumb: if your total deductions are below about ₹4 lakh, the **New Regime** usually saves more; if you fully use 80C + 80D + HRA + home-loan interest, the **Old Regime** often wins.
+**Step 2 — Under the Old Regime**, the main levers are: Section 80C up to ₹1,50,000 (PF, PPF, ELSS, LIC, tuition fees, home-loan principal); Section 80CCD(1B) additional ₹50,000 in NPS; Section 80D up to ₹1,00,000 (health insurance for you and senior-citizen parents); Section 24(b) up to ₹2,00,000 (self-occupied home-loan interest); HRA exemption (rent receipts + landlord PAN if rent &gt; ₹1L/year); Section 80E (full education-loan interest, no upper cap).
+**Step 3 — Under both regimes**, two Koenig-specific perks remain: **Meal Passes / Sodexo** (₹1,05,600 tax-free per year) and **Employer NPS 80CCD(2)** (employer contribution, no cap on employee's side).
+**Step 4 — Declare your investments** to the Tax team at tax@koenig-solutions.com so TDS is computed correctly through the year.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Here is how Koenig employees can save tax for FY 2026-27:
+**Step 1 — Choose the right regime.** Use the in-app **Tax Calculator** (Start Here → 🧮 Tax Calculator) to compare your liability under both regimes. As a rough rule of thumb: if your total deductions are below about ₹4 lakh, the **New Regime** usually saves more; if you fully use 80C + 80D + HRA + home-loan interest, the **Old Regime** often wins.
+**Step 2 — Under the Old Regime**, the main levers are: Section 80C up to ₹1,50,000 (PF, PPF, ELSS, LIC, tuition fees, home-loan principal); Section 80CCD(1B) additional ₹50,000 in NPS; Section 80D up to ₹1,00,000 (health insurance for you and senior-citizen parents); Section 24(b) up to ₹2,00,000 (self-occupied home-loan interest); HRA exemption (rent receipts + landlord PAN if rent &gt; ₹1L/year); Section 80E (full education-loan interest, no upper cap).
+**Step 3 — Under both regimes**, two Koenig-specific perks remain: **Meal Passes / Sodexo** (₹1,05,600 tax-free per year) and **Employer NPS 80CCD(2)** (employer contribution, no cap on employee's side).
+**Step 4 — Declare your investments** to the Tax team at tax@koenig-solutions.com so TDS is computed correctly through the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>How can I save tax under the New Regime?</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>save tax new regime; reduce tax new regime; new regime tax planning; new tax regime savings</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>save, new regime, meal passes, 80CCD(2)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Under the New Regime for FY 2026-27 most traditional deductions (80C, 80D, HRA, LTA, home-loan interest, etc.) are NOT available. The savings levers that DO apply are:
+1. **Standard Deduction** ₹75,000 (automatically applied to salary)
+2. **Section 87A rebate** — taxable income up to ₹12,00,000 becomes NIL tax
+3. **Meal Passes / Sodexo** ₹1,05,600 per year — tax-free perquisite
+4. **Employer NPS 80CCD(2)** — employer's contribution is tax-free in your hands (up to 14% of Basic for govt employees, 10% of Basic for others)
+5. **Gratuity, leave encashment on retirement** — statutory exemptions still apply
+If your annual gross is below about ₹13 L the New Regime usually beats the Old one. Use Start Here → 🧮 Tax Calculator to confirm for your salary.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Under the New Regime for FY 2026-27 most traditional deductions (80C, 80D, HRA, LTA, home-loan interest, etc.) are NOT available. The savings levers that DO apply are:
+1. **Standard Deduction** ₹75,000 (automatically applied to salary)
+2. **Section 87A rebate** — taxable income up to ₹12,00,000 becomes NIL tax
+3. **Meal Passes / Sodexo** ₹1,05,600 per year — tax-free perquisite
+4. **Employer NPS 80CCD(2)** — employer's contribution is tax-free in your hands (up to 14% of Basic for govt employees, 10% of Basic for others)
+5. **Gratuity, leave encashment on retirement** — statutory exemptions still apply
+If your annual gross is below about ₹13 L the New Regime usually beats the Old one. Use Start Here → 🧮 Tax Calculator to confirm for your salary.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Under the New Regime for FY 2026-27 most traditional deductions (80C, 80D, HRA, LTA, home-loan interest, etc.) are NOT available. The savings levers that DO apply are:
+1. **Standard Deduction** ₹75,000 (automatically applied to salary)
+2. **Section 87A rebate** — taxable income up to ₹12,00,000 becomes NIL tax
+3. **Meal Passes / Sodexo** ₹1,05,600 per year — tax-free perquisite
+4. **Employer NPS 80CCD(2)** — employer's contribution is tax-free in your hands (up to 14% of Basic for govt employees, 10% of Basic for others)
+5. **Gratuity, leave encashment on retirement** — statutory exemptions still apply
+If your annual gross is below about ₹13 L the New Regime usually beats the Old one. Use Start Here → 🧮 Tax Calculator to confirm for your salary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>How can I save tax under the Old Regime?</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>save tax old regime; reduce tax old regime; old regime planning; how to use 80C 80D</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>save, old regime, 80C, 80D, HRA, NPS</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Old-Regime tax-saving levers for FY 2026-27 (combine as many as you qualify for):
+**Section 80C** — up to ₹1,50,000: EPF, PPF, ELSS, life insurance premium, NSC, 5-year tax-saving FD, Sukanya Samriddhi, home-loan principal, children's tuition fees.
+**Section 80CCD(1B)** — additional ₹50,000 in NPS Tier 1 (over and above the 80C limit).
+**Section 80D** — health insurance premium: ₹25,000 for self/family + ₹25,000 for parents (₹50,000 each if senior citizens). Maximum ₹1,00,000.
+**Section 24(b)** — home-loan interest up to ₹2,00,000 (self-occupied property).
+**HRA exemption** — least of (actual HRA, rent − 10% of Basic, 50%/40% of Basic). Submit rent receipts.
+**Section 80E** — full education-loan interest for up to 8 years.
+**Section 80G** — donations to approved charities (50% or 100%, cash &gt; ₹2,000 disallowed).
+**Standard Deduction** of ₹50,000 from salary is automatic.
+Also retain Meal Passes (₹1,05,600) and Employer NPS 80CCD(2) — those work under both regimes.
+Use Start Here → 🧮 Tax Calculator to see your exact saving.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Old-Regime tax-saving levers for FY 2026-27 (combine as many as you qualify for):
+**Section 80C** — up to ₹1,50,000: EPF, PPF, ELSS, life insurance premium, NSC, 5-year tax-saving FD, Sukanya Samriddhi, home-loan principal, children's tuition fees.
+**Section 80CCD(1B)** — additional ₹50,000 in NPS Tier 1 (over and above the 80C limit).
+**Section 80D** — health insurance premium: ₹25,000 for self/family + ₹25,000 for parents (₹50,000 each if senior citizens). Maximum ₹1,00,000.
+**Section 24(b)** — home-loan interest up to ₹2,00,000 (self-occupied property).
+**HRA exemption** — least of (actual HRA, rent − 10% of Basic, 50%/40% of Basic). Submit rent receipts.
+**Section 80E** — full education-loan interest for up to 8 years.
+**Section 80G** — donations to approved charities (50% or 100%, cash &gt; ₹2,000 disallowed).
+**Standard Deduction** of ₹50,000 from salary is automatic.
+Also retain Meal Passes (₹1,05,600) and Employer NPS 80CCD(2) — those work under both regimes.
+Use Start Here → 🧮 Tax Calculator to see your exact saving.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Old-Regime tax-saving levers for FY 2026-27 (combine as many as you qualify for):
+**Section 80C** — up to ₹1,50,000: EPF, PPF, ELSS, life insurance premium, NSC, 5-year tax-saving FD, Sukanya Samriddhi, home-loan principal, children's tuition fees.
+**Section 80CCD(1B)** — additional ₹50,000 in NPS Tier 1 (over and above the 80C limit).
+**Section 80D** — health insurance premium: ₹25,000 for self/family + ₹25,000 for parents (₹50,000 each if senior citizens). Maximum ₹1,00,000.
+**Section 24(b)** — home-loan interest up to ₹2,00,000 (self-occupied property).
+**HRA exemption** — least of (actual HRA, rent − 10% of Basic, 50%/40% of Basic). Submit rent receipts.
+**Section 80E** — full education-loan interest for up to 8 years.
+**Section 80G** — donations to approved charities (50% or 100%, cash &gt; ₹2,000 disallowed).
+**Standard Deduction** of ₹50,000 from salary is automatic.
+Also retain Meal Passes (₹1,05,600) and Employer NPS 80CCD(2) — those work under both regimes.
+Use Start Here → 🧮 Tax Calculator to see your exact saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>What is the Koenig salary structure?</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>salary breakup; salary components; how is my salary divided; salary structure koenig; CTC breakup</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>salary, structure, breakup, basic, HRA, components</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Standard Koenig salary structure for the year, expressed as percentages of your annual CTC:
+• **Basic** — 50% of total CTC
+• **HRA** — 50% of Basic (i.e., 25% of total CTC)
+• **Meal Passes / Sodexo** — ₹1,05,600 per year (fixed)
+• **Telephone / Internet Reimbursement** — 3% of total
+• **Electricity Reimbursement** — 3% of total
+• **Professional / Software Reimbursement** — 2% of total
+• **Skill Development** — 2% of total
+• **Power &amp; Utility Allowance** — 2% of total
+• **Taxable Allowance** — whatever is left after the above
+Open Start Here → 🧮 Tax Calculator → tick the “View Koenig salary-structure breakdown” expander to see the exact split for your CTC.
+Note: at lower CTC levels the Meal Passes amount is proportionally reduced so the components fit within the gross.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Standard Koenig salary structure for the year, expressed as percentages of your annual CTC:
+• **Basic** — 50% of total CTC
+• **HRA** — 50% of Basic (i.e., 25% of total CTC)
+• **Meal Passes / Sodexo** — ₹1,05,600 per year (fixed)
+• **Telephone / Internet Reimbursement** — 3% of total
+• **Electricity Reimbursement** — 3% of total
+• **Professional / Software Reimbursement** — 2% of total
+• **Skill Development** — 2% of total
+• **Power &amp; Utility Allowance** — 2% of total
+• **Taxable Allowance** — whatever is left after the above
+Open Start Here → 🧮 Tax Calculator → tick the “View Koenig salary-structure breakdown” expander to see the exact split for your CTC.
+Note: at lower CTC levels the Meal Passes amount is proportionally reduced so the components fit within the gross.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Standard Koenig salary structure for the year, expressed as percentages of your annual CTC:
+• **Basic** — 50% of total CTC
+• **HRA** — 50% of Basic (i.e., 25% of total CTC)
+• **Meal Passes / Sodexo** — ₹1,05,600 per year (fixed)
+• **Telephone / Internet Reimbursement** — 3% of total
+• **Electricity Reimbursement** — 3% of total
+• **Professional / Software Reimbursement** — 2% of total
+• **Skill Development** — 2% of total
+• **Power &amp; Utility Allowance** — 2% of total
+• **Taxable Allowance** — whatever is left after the above
+Open Start Here → 🧮 Tax Calculator → tick the “View Koenig salary-structure breakdown” expander to see the exact split for your CTC.
+Note: at lower CTC levels the Meal Passes amount is proportionally reduced so the components fit within the gross.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Are Meal Passes / Sodexo taxable?</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>meal passes tax; sodexo taxable; food coupon tax; meal voucher tax free</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>meal passes, sodexo, food coupon, tax-free</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>**Meal Passes / Sodexo coupons are tax-free** under both the Old and the New Tax Regime, as a perquisite under Rule 3(7)(iii) of the Income-tax Rules.
+Koenig provides up to ₹1,05,600 per year (typically ₹50 per meal × 2 meals per working day × 22 working days × 12 months). The full amount is exempt from income tax — no declaration or proof submission is needed, since payroll provides the coupons directly.
+This is one of the very few perks that survives under the New Regime, so it's a useful tax-saving lever for everyone.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>**Meal Passes / Sodexo coupons are tax-free** under both the Old and the New Tax Regime, as a perquisite under Rule 3(7)(iii) of the Income-tax Rules.
+Koenig provides up to ₹1,05,600 per year (typically ₹50 per meal × 2 meals per working day × 22 working days × 12 months). The full amount is exempt from income tax — no declaration or proof submission is needed, since payroll provides the coupons directly.
+This is one of the very few perks that survives under the New Regime, so it's a useful tax-saving lever for everyone.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>**Meal Passes / Sodexo coupons are tax-free** under both the Old and the New Tax Regime, as a perquisite under Rule 3(7)(iii) of the Income-tax Rules.
+Koenig provides up to ₹1,05,600 per year (typically ₹50 per meal × 2 meals per working day × 22 working days × 12 months). The full amount is exempt from income tax — no declaration or proof submission is needed, since payroll provides the coupons directly.
+This is one of the very few perks that survives under the New Regime, so it's a useful tax-saving lever for everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tax Regime</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Is Employer NPS contribution taxable?</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>employer NPS taxable; 80CCD(2) tax; employer NPS contribution tax free; corporate NPS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>employer NPS, 80CCD(2), corporate NPS, tax-free</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>**Employer NPS contribution under Section 80CCD(2) is tax-free in the employee's hands** under BOTH the Old and New Tax Regimes. There is no upper rupee limit, but the deduction is capped at:
+• **14% of Basic salary** for central government employees
+• **10% of Basic salary** for private-sector employees
+This is in addition to your own NPS contribution under 80CCD(1)/(1B) (Old Regime only). To start or modify employer NPS, reach out to the Tax / Payroll team at tax@koenig-solutions.com.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>**Employer NPS contribution under Section 80CCD(2) is tax-free in the employee's hands** under BOTH the Old and New Tax Regimes. There is no upper rupee limit, but the deduction is capped at:
+• **14% of Basic salary** for central government employees
+• **10% of Basic salary** for private-sector employees
+This is in addition to your own NPS contribution under 80CCD(1)/(1B) (Old Regime only). To start or modify employer NPS, reach out to the Tax / Payroll team at tax@koenig-solutions.com.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Tax Team</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>tax@koenig-solutions.com</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>**Employer NPS contribution under Section 80CCD(2) is tax-free in the employee's hands** under BOTH the Old and New Tax Regimes. There is no upper rupee limit, but the deduction is capped at:
+• **14% of Basic salary** for central government employees
+• **10% of Basic salary** for private-sector employees
+This is in addition to your own NPS contribution under 80CCD(1)/(1B) (Old Regime only). To start or modify employer NPS, reach out to the Tax / Payroll team at tax@koenig-solutions.com.</t>
         </is>
       </c>
     </row>

--- a/knowledge/Koenig_VoiceBot_FAQ_Master.xlsx
+++ b/knowledge/Koenig_VoiceBot_FAQ_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/praveenchaudhary/Downloads/Koenig-Strides-speed/knowledge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B779608-BC5D-F94A-879B-6B86FAF74936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6B9856-8E5C-CF43-8D84-144DE3447047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="1906">
   <si>
     <t>KOENIG VOICE BOT — FAQ MASTER FILE</t>
   </si>
@@ -3739,12 +3739,6 @@
     <t>The India entity is Koenig Solutions Pvt Ltd.</t>
   </si>
   <si>
-    <t>Jony Saini</t>
-  </si>
-  <si>
-    <t>jony.saini@koenig-solutions.com</t>
-  </si>
-  <si>
     <t>Where is the head office of Koenig India?</t>
   </si>
   <si>
@@ -3808,9 +3802,6 @@
     <t>U72200DL1993PTC053242</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India entity details.</t>
-  </si>
-  <si>
     <t>What is the PAN of Koenig India?</t>
   </si>
   <si>
@@ -4081,9 +4072,6 @@
     <t>30AABCK9007D1Z5</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India Goa entity details.</t>
-  </si>
-  <si>
     <t>Entity – Koenig India Branch Dehradun</t>
   </si>
   <si>
@@ -4129,9 +4117,6 @@
     <t>05AABCK9007D1ZY</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India Dehradun entity details.</t>
-  </si>
-  <si>
     <t>Entity – Koenig India Branch Bangalore</t>
   </si>
   <si>
@@ -4177,9 +4162,6 @@
     <t>29AABCK9007D1ZO</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India Bangalore entity details.</t>
-  </si>
-  <si>
     <t>Entity – Koenig India Branch Chennai</t>
   </si>
   <si>
@@ -4225,9 +4207,6 @@
     <t>33AABCK9007D1ZZ</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India Chennai entity details.</t>
-  </si>
-  <si>
     <t>Entity – Koenig India Branch Gurgaon</t>
   </si>
   <si>
@@ -4273,9 +4252,6 @@
     <t>06AABCK9007D1ZW</t>
   </si>
   <si>
-    <t>This information is protected. Please contact Jony Saini at jony.saini@koenig-solutions.com for Koenig India Gurgaon entity details.</t>
-  </si>
-  <si>
     <t>Entity – UAE FZ LLC (Dubai)</t>
   </si>
   <si>
@@ -5780,13 +5756,34 @@
   </si>
   <si>
     <t>Pooja.Prasad@koenig-solutions.com</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad	 at Pooja.Prasad@koenig-solutions.com for Koenig India entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad	 at Pooja.Prasad@koenig-solutions.com for Koenig India Gurgaon entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad	 at Pooja.Prasad@koenig-solutions.com for Koenig India Chennai entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad at Pooja.Prasad@koenig-solutions.com for Koenig India Bangalore entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad at Pooja.Prasad@koenig-solutions.com for Koenig India Dehradun entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad at Pooja.Prasad@koenig-solutions.com for Koenig India Goa entity details.</t>
+  </si>
+  <si>
+    <t>This information is protected. Please contact Pooja Parsad at Pooja.Prasad@koenig-solutions.com for Koenig India entity details.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5804,6 +5801,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5845,12 +5849,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -15438,10 +15443,10 @@
         <v>44</v>
       </c>
       <c r="I128" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J128" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K128" t="s">
         <v>1225</v>
@@ -15455,31 +15460,31 @@
         <v>1221</v>
       </c>
       <c r="C129" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E129" t="s">
         <v>1228</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1230</v>
       </c>
       <c r="F129" t="s">
         <v>912</v>
       </c>
       <c r="G129" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="H129" t="s">
         <v>44</v>
       </c>
       <c r="I129" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J129" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K129" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
@@ -15490,31 +15495,31 @@
         <v>1221</v>
       </c>
       <c r="C130" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E130" t="s">
         <v>1232</v>
       </c>
-      <c r="D130" t="s">
+      <c r="F130" t="s">
         <v>1233</v>
       </c>
-      <c r="E130" t="s">
+      <c r="G130" t="s">
         <v>1234</v>
       </c>
-      <c r="F130" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G130" t="s">
-        <v>1236</v>
-      </c>
       <c r="H130" t="s">
         <v>44</v>
       </c>
       <c r="I130" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J130" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K130" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
@@ -15525,31 +15530,31 @@
         <v>1221</v>
       </c>
       <c r="C131" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E131" t="s">
         <v>1237</v>
       </c>
-      <c r="D131" t="s">
+      <c r="F131" t="s">
         <v>1238</v>
       </c>
-      <c r="E131" t="s">
+      <c r="G131" t="s">
         <v>1239</v>
       </c>
-      <c r="F131" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G131" t="s">
-        <v>1241</v>
-      </c>
       <c r="H131" t="s">
         <v>44</v>
       </c>
       <c r="I131" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J131" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K131" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
@@ -15560,13 +15565,13 @@
         <v>1221</v>
       </c>
       <c r="C132" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E132" t="s">
         <v>1242</v>
-      </c>
-      <c r="D132" t="s">
-        <v>1243</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1244</v>
       </c>
       <c r="F132" t="s">
         <v>696</v>
@@ -15578,10 +15583,10 @@
         <v>44</v>
       </c>
       <c r="I132" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J132" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K132" t="s">
         <v>927</v>
@@ -15595,31 +15600,31 @@
         <v>1221</v>
       </c>
       <c r="C133" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E133" t="s">
         <v>1245</v>
       </c>
-      <c r="D133" t="s">
+      <c r="F133" t="s">
         <v>1246</v>
       </c>
-      <c r="E133" t="s">
-        <v>1247</v>
-      </c>
-      <c r="F133" t="s">
-        <v>1248</v>
-      </c>
       <c r="G133" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H133" t="s">
         <v>703</v>
       </c>
       <c r="I133" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J133" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K133" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K133" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
@@ -15630,31 +15635,31 @@
         <v>1221</v>
       </c>
       <c r="C134" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F134" t="s">
         <v>1250</v>
       </c>
-      <c r="D134" t="s">
-        <v>1251</v>
-      </c>
-      <c r="E134" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F134" t="s">
-        <v>1253</v>
-      </c>
       <c r="G134" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H134" t="s">
         <v>703</v>
       </c>
       <c r="I134" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J134" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K134" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
@@ -15665,31 +15670,31 @@
         <v>1221</v>
       </c>
       <c r="C135" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="D135" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="E135" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="F135" t="s">
         <v>944</v>
       </c>
       <c r="G135" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H135" t="s">
         <v>703</v>
       </c>
       <c r="I135" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J135" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K135" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K135" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
@@ -15700,13 +15705,13 @@
         <v>1221</v>
       </c>
       <c r="C136" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="D136" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E136" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F136" t="s">
         <v>948</v>
@@ -15718,10 +15723,10 @@
         <v>44</v>
       </c>
       <c r="I136" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J136" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K136" t="s">
         <v>949</v>
@@ -15735,31 +15740,31 @@
         <v>1221</v>
       </c>
       <c r="C137" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="D137" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="E137" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="F137" t="s">
         <v>953</v>
       </c>
       <c r="G137" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H137" t="s">
         <v>703</v>
       </c>
       <c r="I137" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J137" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K137" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K137" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
@@ -15770,31 +15775,31 @@
         <v>1221</v>
       </c>
       <c r="C138" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F138" t="s">
         <v>1263</v>
       </c>
-      <c r="D138" t="s">
-        <v>1264</v>
-      </c>
-      <c r="E138" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F138" t="s">
-        <v>1266</v>
-      </c>
       <c r="G138" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H138" t="s">
         <v>703</v>
       </c>
       <c r="I138" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J138" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K138" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
@@ -15805,31 +15810,31 @@
         <v>1221</v>
       </c>
       <c r="C139" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F139" t="s">
         <v>1267</v>
       </c>
-      <c r="D139" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E139" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F139" t="s">
-        <v>1270</v>
-      </c>
       <c r="G139" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H139" t="s">
         <v>703</v>
       </c>
       <c r="I139" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J139" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K139" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
@@ -15840,31 +15845,31 @@
         <v>1221</v>
       </c>
       <c r="C140" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F140" t="s">
         <v>1271</v>
       </c>
-      <c r="D140" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E140" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F140" t="s">
-        <v>1274</v>
-      </c>
       <c r="G140" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H140" t="s">
         <v>703</v>
       </c>
       <c r="I140" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J140" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K140" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
@@ -15875,31 +15880,31 @@
         <v>1221</v>
       </c>
       <c r="C141" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E141" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F141" t="s">
         <v>1275</v>
       </c>
-      <c r="D141" t="s">
+      <c r="G141" t="s">
         <v>1276</v>
       </c>
-      <c r="E141" t="s">
-        <v>1277</v>
-      </c>
-      <c r="F141" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G141" t="s">
-        <v>1279</v>
-      </c>
       <c r="H141" t="s">
         <v>44</v>
       </c>
       <c r="I141" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J141" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K141" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -15910,13 +15915,13 @@
         <v>1221</v>
       </c>
       <c r="C142" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="D142" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="E142" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F142" t="s">
         <v>974</v>
@@ -15928,10 +15933,10 @@
         <v>44</v>
       </c>
       <c r="I142" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J142" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K142" t="s">
         <v>975</v>
@@ -15945,31 +15950,31 @@
         <v>1221</v>
       </c>
       <c r="C143" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E143" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F143" t="s">
         <v>1283</v>
       </c>
-      <c r="D143" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E143" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F143" t="s">
-        <v>1286</v>
-      </c>
       <c r="G143" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H143" t="s">
         <v>703</v>
       </c>
       <c r="I143" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J143" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K143" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
@@ -15980,31 +15985,31 @@
         <v>1221</v>
       </c>
       <c r="C144" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E144" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F144" t="s">
         <v>1287</v>
       </c>
-      <c r="D144" t="s">
-        <v>1288</v>
-      </c>
-      <c r="E144" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F144" t="s">
-        <v>1290</v>
-      </c>
       <c r="G144" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H144" t="s">
         <v>703</v>
       </c>
       <c r="I144" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J144" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K144" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
@@ -16015,31 +16020,31 @@
         <v>1221</v>
       </c>
       <c r="C145" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F145" t="s">
         <v>1291</v>
       </c>
-      <c r="D145" t="s">
-        <v>1292</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1293</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1294</v>
-      </c>
       <c r="G145" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H145" t="s">
         <v>703</v>
       </c>
       <c r="I145" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J145" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K145" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
@@ -16050,31 +16055,31 @@
         <v>1221</v>
       </c>
       <c r="C146" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="D146" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="E146" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="F146" t="s">
         <v>824</v>
       </c>
       <c r="G146" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H146" t="s">
         <v>703</v>
       </c>
       <c r="I146" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J146" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K146" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K146" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
@@ -16085,31 +16090,31 @@
         <v>1221</v>
       </c>
       <c r="C147" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F147" t="s">
         <v>1298</v>
       </c>
-      <c r="D147" t="s">
-        <v>1299</v>
-      </c>
-      <c r="E147" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1301</v>
-      </c>
       <c r="G147" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H147" t="s">
         <v>703</v>
       </c>
       <c r="I147" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J147" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K147" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
@@ -16120,31 +16125,31 @@
         <v>1221</v>
       </c>
       <c r="C148" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F148" t="s">
         <v>1302</v>
       </c>
-      <c r="D148" t="s">
-        <v>1303</v>
-      </c>
-      <c r="E148" t="s">
-        <v>1304</v>
-      </c>
-      <c r="F148" t="s">
-        <v>1305</v>
-      </c>
       <c r="G148" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H148" t="s">
         <v>703</v>
       </c>
       <c r="I148" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J148" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K148" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K148" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
@@ -16155,31 +16160,31 @@
         <v>1221</v>
       </c>
       <c r="C149" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F149" t="s">
         <v>1306</v>
       </c>
-      <c r="D149" t="s">
-        <v>1307</v>
-      </c>
-      <c r="E149" t="s">
-        <v>1308</v>
-      </c>
-      <c r="F149" t="s">
-        <v>1309</v>
-      </c>
       <c r="G149" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H149" t="s">
         <v>703</v>
       </c>
       <c r="I149" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J149" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K149" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
@@ -16190,31 +16195,31 @@
         <v>1221</v>
       </c>
       <c r="C150" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E150" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F150" t="s">
         <v>1310</v>
       </c>
-      <c r="D150" t="s">
-        <v>1311</v>
-      </c>
-      <c r="E150" t="s">
-        <v>1312</v>
-      </c>
-      <c r="F150" t="s">
-        <v>1313</v>
-      </c>
       <c r="G150" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H150" t="s">
         <v>703</v>
       </c>
       <c r="I150" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J150" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K150" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
@@ -16225,31 +16230,31 @@
         <v>1221</v>
       </c>
       <c r="C151" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E151" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F151" t="s">
         <v>1314</v>
       </c>
-      <c r="D151" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E151" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F151" t="s">
-        <v>1317</v>
-      </c>
       <c r="G151" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H151" t="s">
         <v>703</v>
       </c>
       <c r="I151" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J151" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K151" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K151" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
@@ -16260,31 +16265,31 @@
         <v>1221</v>
       </c>
       <c r="C152" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="D152" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="E152" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="F152" t="s">
         <v>1023</v>
       </c>
       <c r="G152" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H152" t="s">
         <v>703</v>
       </c>
       <c r="I152" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J152" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K152" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K152" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
@@ -16295,31 +16300,31 @@
         <v>1221</v>
       </c>
       <c r="C153" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E153" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F153" t="s">
         <v>1321</v>
       </c>
-      <c r="D153" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E153" t="s">
-        <v>1323</v>
-      </c>
-      <c r="F153" t="s">
-        <v>1324</v>
-      </c>
       <c r="G153" t="s">
-        <v>1249</v>
+        <v>1899</v>
       </c>
       <c r="H153" t="s">
         <v>703</v>
       </c>
       <c r="I153" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J153" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K153" t="s">
-        <v>1249</v>
+        <v>1897</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K153" s="3" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
@@ -16327,34 +16332,34 @@
         <v>254</v>
       </c>
       <c r="B154" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E154" t="s">
         <v>1325</v>
       </c>
-      <c r="C154" t="s">
+      <c r="F154" t="s">
         <v>1326</v>
       </c>
-      <c r="D154" t="s">
+      <c r="G154" t="s">
         <v>1327</v>
       </c>
-      <c r="E154" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1330</v>
-      </c>
       <c r="H154" t="s">
         <v>44</v>
       </c>
       <c r="I154" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J154" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K154" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
@@ -16362,34 +16367,34 @@
         <v>255</v>
       </c>
       <c r="B155" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C155" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E155" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F155" t="s">
         <v>1331</v>
       </c>
-      <c r="D155" t="s">
+      <c r="G155" t="s">
         <v>1332</v>
       </c>
-      <c r="E155" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F155" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G155" t="s">
-        <v>1335</v>
-      </c>
       <c r="H155" t="s">
         <v>44</v>
       </c>
       <c r="I155" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J155" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K155" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
@@ -16397,34 +16402,34 @@
         <v>256</v>
       </c>
       <c r="B156" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C156" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E156" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F156" t="s">
         <v>1336</v>
       </c>
-      <c r="D156" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E156" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F156" t="s">
-        <v>1339</v>
-      </c>
       <c r="G156" t="s">
-        <v>1340</v>
+        <v>1899</v>
       </c>
       <c r="H156" t="s">
         <v>703</v>
       </c>
       <c r="I156" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J156" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K156" t="s">
-        <v>1340</v>
+        <v>1897</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K156" s="3" t="s">
+        <v>1904</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
@@ -16432,34 +16437,34 @@
         <v>257</v>
       </c>
       <c r="B157" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F157" t="s">
         <v>1341</v>
       </c>
-      <c r="C157" t="s">
+      <c r="G157" t="s">
         <v>1342</v>
       </c>
-      <c r="D157" t="s">
-        <v>1343</v>
-      </c>
-      <c r="E157" t="s">
-        <v>1344</v>
-      </c>
-      <c r="F157" t="s">
-        <v>1345</v>
-      </c>
-      <c r="G157" t="s">
-        <v>1346</v>
-      </c>
       <c r="H157" t="s">
         <v>44</v>
       </c>
       <c r="I157" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J157" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K157" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
@@ -16467,34 +16472,34 @@
         <v>258</v>
       </c>
       <c r="B158" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C158" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E158" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F158" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G158" t="s">
         <v>1347</v>
       </c>
-      <c r="D158" t="s">
-        <v>1348</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1349</v>
-      </c>
-      <c r="F158" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G158" t="s">
-        <v>1351</v>
-      </c>
       <c r="H158" t="s">
         <v>44</v>
       </c>
       <c r="I158" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J158" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K158" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.2">
@@ -16502,34 +16507,34 @@
         <v>259</v>
       </c>
       <c r="B159" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C159" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D159" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E159" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="F159" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="G159" t="s">
-        <v>1356</v>
+        <v>1899</v>
       </c>
       <c r="H159" t="s">
         <v>703</v>
       </c>
       <c r="I159" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J159" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K159" t="s">
-        <v>1356</v>
+        <v>1897</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>1903</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
@@ -16537,34 +16542,34 @@
         <v>260</v>
       </c>
       <c r="B160" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D160" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E160" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G160" t="s">
         <v>1357</v>
       </c>
-      <c r="C160" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1359</v>
-      </c>
-      <c r="E160" t="s">
-        <v>1360</v>
-      </c>
-      <c r="F160" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G160" t="s">
-        <v>1362</v>
-      </c>
       <c r="H160" t="s">
         <v>44</v>
       </c>
       <c r="I160" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J160" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K160" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
@@ -16572,34 +16577,34 @@
         <v>261</v>
       </c>
       <c r="B161" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="C161" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="D161" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="E161" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="F161" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="G161" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="H161" t="s">
         <v>44</v>
       </c>
       <c r="I161" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J161" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K161" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
@@ -16607,34 +16612,34 @@
         <v>262</v>
       </c>
       <c r="B162" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="C162" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="D162" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="E162" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="F162" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="G162" t="s">
-        <v>1372</v>
+        <v>1899</v>
       </c>
       <c r="H162" t="s">
         <v>703</v>
       </c>
       <c r="I162" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J162" t="s">
-        <v>1227</v>
-      </c>
-      <c r="K162" t="s">
-        <v>1372</v>
+        <v>1897</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K162" s="3" t="s">
+        <v>1902</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
@@ -16642,34 +16647,34 @@
         <v>263</v>
       </c>
       <c r="B163" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="C163" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="D163" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="E163" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="F163" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="G163" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="H163" t="s">
         <v>44</v>
       </c>
       <c r="I163" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J163" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K163" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
@@ -16677,34 +16682,34 @@
         <v>264</v>
       </c>
       <c r="B164" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C164" t="s">
         <v>1373</v>
       </c>
-      <c r="C164" t="s">
-        <v>1379</v>
-      </c>
       <c r="D164" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="E164" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="F164" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="G164" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="H164" t="s">
         <v>44</v>
       </c>
       <c r="I164" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J164" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K164" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
@@ -16712,34 +16717,34 @@
         <v>265</v>
       </c>
       <c r="B165" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="C165" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="D165" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="E165" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F165" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="G165" t="s">
-        <v>1388</v>
+        <v>1899</v>
       </c>
       <c r="H165" t="s">
         <v>703</v>
       </c>
       <c r="I165" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J165" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K165" t="s">
-        <v>1388</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
@@ -16747,34 +16752,34 @@
         <v>266</v>
       </c>
       <c r="B166" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="C166" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="D166" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="E166" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="F166" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="G166" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="H166" t="s">
         <v>44</v>
       </c>
       <c r="I166" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J166" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K166" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.2">
@@ -16782,34 +16787,34 @@
         <v>267</v>
       </c>
       <c r="B167" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D167" t="s">
         <v>1389</v>
       </c>
-      <c r="C167" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D167" t="s">
-        <v>1396</v>
-      </c>
       <c r="E167" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="F167" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="G167" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="H167" t="s">
         <v>44</v>
       </c>
       <c r="I167" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J167" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K167" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
@@ -16817,34 +16822,34 @@
         <v>268</v>
       </c>
       <c r="B168" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="C168" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="D168" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="E168" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="F168" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="G168" t="s">
-        <v>1404</v>
+        <v>1899</v>
       </c>
       <c r="H168" t="s">
         <v>703</v>
       </c>
       <c r="I168" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J168" t="s">
-        <v>1227</v>
+        <v>1897</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>1898</v>
       </c>
       <c r="K168" t="s">
-        <v>1404</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
@@ -16852,34 +16857,34 @@
         <v>269</v>
       </c>
       <c r="B169" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C169" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
       <c r="D169" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="E169" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="F169" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="G169" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="H169" t="s">
         <v>44</v>
       </c>
       <c r="I169" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J169" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K169" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
@@ -16887,34 +16892,34 @@
         <v>270</v>
       </c>
       <c r="B170" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C170" t="s">
         <v>1405</v>
       </c>
-      <c r="C170" t="s">
-        <v>1413</v>
-      </c>
       <c r="D170" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="E170" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="F170" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="G170" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="H170" t="s">
         <v>44</v>
       </c>
       <c r="I170" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J170" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K170" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
@@ -16922,34 +16927,34 @@
         <v>271</v>
       </c>
       <c r="B171" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C171" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="D171" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="E171" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="F171" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="G171" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="H171" t="s">
         <v>44</v>
       </c>
       <c r="I171" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J171" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K171" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
@@ -16957,34 +16962,34 @@
         <v>272</v>
       </c>
       <c r="B172" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C172" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="D172" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="E172" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
       <c r="F172" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="G172" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="H172" t="s">
         <v>44</v>
       </c>
       <c r="I172" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J172" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K172" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
@@ -16992,34 +16997,34 @@
         <v>273</v>
       </c>
       <c r="B173" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C173" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="D173" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="E173" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="F173" t="s">
         <v>853</v>
       </c>
       <c r="G173" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="H173" t="s">
         <v>44</v>
       </c>
       <c r="I173" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J173" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K173" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
@@ -17027,34 +17032,34 @@
         <v>274</v>
       </c>
       <c r="B174" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C174" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="D174" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="E174" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
       <c r="F174" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="G174" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H174" t="s">
         <v>703</v>
       </c>
       <c r="I174" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J174" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K174" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
@@ -17062,34 +17067,34 @@
         <v>275</v>
       </c>
       <c r="B175" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C175" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="D175" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
       <c r="E175" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="F175" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="G175" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H175" t="s">
         <v>703</v>
       </c>
       <c r="I175" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J175" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K175" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
@@ -17097,34 +17102,34 @@
         <v>276</v>
       </c>
       <c r="B176" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C176" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="D176" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="E176" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="F176" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="G176" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H176" t="s">
         <v>703</v>
       </c>
       <c r="I176" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J176" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K176" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
@@ -17132,34 +17137,34 @@
         <v>277</v>
       </c>
       <c r="B177" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C177" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="D177" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="E177" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="F177" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="G177" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="H177" t="s">
         <v>44</v>
       </c>
       <c r="I177" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J177" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K177" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
@@ -17167,34 +17172,34 @@
         <v>278</v>
       </c>
       <c r="B178" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C178" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="D178" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="E178" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="F178" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="G178" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H178" t="s">
         <v>703</v>
       </c>
       <c r="I178" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J178" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K178" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
@@ -17202,34 +17207,34 @@
         <v>279</v>
       </c>
       <c r="B179" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C179" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="D179" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="E179" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="F179" t="s">
         <v>1148</v>
       </c>
       <c r="G179" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H179" t="s">
         <v>703</v>
       </c>
       <c r="I179" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J179" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K179" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
@@ -17237,34 +17242,34 @@
         <v>280</v>
       </c>
       <c r="B180" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C180" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="D180" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
       <c r="E180" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
       <c r="F180" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
       <c r="G180" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H180" t="s">
         <v>703</v>
       </c>
       <c r="I180" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J180" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K180" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
@@ -17272,34 +17277,34 @@
         <v>281</v>
       </c>
       <c r="B181" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C181" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
       <c r="D181" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
       <c r="E181" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
       <c r="F181" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
       <c r="G181" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="H181" t="s">
         <v>44</v>
       </c>
       <c r="I181" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J181" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K181" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
@@ -17307,34 +17312,34 @@
         <v>282</v>
       </c>
       <c r="B182" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C182" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="D182" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
       <c r="E182" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
       <c r="F182" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
       <c r="G182" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H182" t="s">
         <v>703</v>
       </c>
       <c r="I182" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J182" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K182" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
@@ -17342,34 +17347,34 @@
         <v>283</v>
       </c>
       <c r="B183" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C183" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="D183" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="E183" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="F183" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="G183" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H183" t="s">
         <v>703</v>
       </c>
       <c r="I183" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J183" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K183" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
@@ -17377,34 +17382,34 @@
         <v>284</v>
       </c>
       <c r="B184" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C184" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="D184" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="E184" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
       <c r="F184" t="s">
         <v>813</v>
       </c>
       <c r="G184" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H184" t="s">
         <v>703</v>
       </c>
       <c r="I184" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J184" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K184" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
@@ -17412,34 +17417,34 @@
         <v>285</v>
       </c>
       <c r="B185" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C185" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="D185" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
       <c r="E185" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="F185" t="s">
         <v>824</v>
       </c>
       <c r="G185" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H185" t="s">
         <v>703</v>
       </c>
       <c r="I185" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J185" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K185" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
@@ -17447,34 +17452,34 @@
         <v>286</v>
       </c>
       <c r="B186" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="C186" t="s">
-        <v>1479</v>
+        <v>1471</v>
       </c>
       <c r="D186" t="s">
-        <v>1480</v>
+        <v>1472</v>
       </c>
       <c r="E186" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
       <c r="F186" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="G186" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="H186" t="s">
         <v>703</v>
       </c>
       <c r="I186" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J186" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K186" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
@@ -17482,34 +17487,34 @@
         <v>287</v>
       </c>
       <c r="B187" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C187" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
       <c r="D187" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
       <c r="E187" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="F187" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
       <c r="G187" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="H187" t="s">
         <v>44</v>
       </c>
       <c r="I187" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J187" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K187" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
@@ -17517,34 +17522,34 @@
         <v>288</v>
       </c>
       <c r="B188" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E188" t="s">
         <v>1482</v>
       </c>
-      <c r="C188" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D188" t="s">
-        <v>1489</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1490</v>
-      </c>
       <c r="F188" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="G188" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="H188" t="s">
         <v>44</v>
       </c>
       <c r="I188" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J188" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K188" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
@@ -17552,34 +17557,34 @@
         <v>289</v>
       </c>
       <c r="B189" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C189" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
       <c r="D189" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
       <c r="E189" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="F189" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
       <c r="G189" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
       <c r="H189" t="s">
         <v>44</v>
       </c>
       <c r="I189" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J189" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K189" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
@@ -17587,34 +17592,34 @@
         <v>290</v>
       </c>
       <c r="B190" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C190" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
       <c r="D190" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="E190" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
       <c r="F190" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="G190" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="H190" t="s">
         <v>44</v>
       </c>
       <c r="I190" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J190" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K190" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
@@ -17622,34 +17627,34 @@
         <v>291</v>
       </c>
       <c r="B191" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C191" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
       <c r="D191" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="E191" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="F191" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
       <c r="G191" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H191" t="s">
         <v>703</v>
       </c>
       <c r="I191" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J191" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K191" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
@@ -17657,34 +17662,34 @@
         <v>292</v>
       </c>
       <c r="B192" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C192" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="D192" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="E192" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="F192" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
       <c r="G192" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H192" t="s">
         <v>703</v>
       </c>
       <c r="I192" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J192" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K192" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
@@ -17692,34 +17697,34 @@
         <v>293</v>
       </c>
       <c r="B193" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C193" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
       <c r="D193" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="E193" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="F193" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="G193" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H193" t="s">
         <v>703</v>
       </c>
       <c r="I193" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J193" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K193" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
@@ -17727,34 +17732,34 @@
         <v>294</v>
       </c>
       <c r="B194" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C194" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="D194" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="E194" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="F194" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="G194" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H194" t="s">
         <v>703</v>
       </c>
       <c r="I194" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J194" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K194" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
@@ -17762,34 +17767,34 @@
         <v>295</v>
       </c>
       <c r="B195" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C195" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="D195" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
       <c r="E195" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
       <c r="F195" t="s">
         <v>1148</v>
       </c>
       <c r="G195" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H195" t="s">
         <v>703</v>
       </c>
       <c r="I195" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J195" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K195" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
@@ -17797,34 +17802,34 @@
         <v>296</v>
       </c>
       <c r="B196" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C196" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="D196" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="E196" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
       <c r="F196" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
       <c r="G196" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H196" t="s">
         <v>703</v>
       </c>
       <c r="I196" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J196" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K196" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
@@ -17832,34 +17837,34 @@
         <v>297</v>
       </c>
       <c r="B197" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C197" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
       <c r="D197" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="E197" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
       <c r="F197" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="G197" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H197" t="s">
         <v>703</v>
       </c>
       <c r="I197" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J197" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K197" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
@@ -17867,34 +17872,34 @@
         <v>298</v>
       </c>
       <c r="B198" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C198" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="D198" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="E198" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="F198" t="s">
         <v>824</v>
       </c>
       <c r="G198" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H198" t="s">
         <v>703</v>
       </c>
       <c r="I198" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J198" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K198" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
@@ -17902,34 +17907,34 @@
         <v>299</v>
       </c>
       <c r="B199" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="C199" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="D199" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="E199" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="F199" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="G199" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="H199" t="s">
         <v>703</v>
       </c>
       <c r="I199" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J199" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K199" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
@@ -17937,22 +17942,22 @@
         <v>300</v>
       </c>
       <c r="B200" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C200" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="D200" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="E200" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="F200" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
       <c r="G200" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
       <c r="H200" t="s">
         <v>44</v>
@@ -17964,7 +17969,7 @@
         <v>677</v>
       </c>
       <c r="K200" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
@@ -17972,22 +17977,22 @@
         <v>301</v>
       </c>
       <c r="B201" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E201" t="s">
         <v>1536</v>
       </c>
-      <c r="C201" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D201" t="s">
-        <v>1543</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1544</v>
-      </c>
       <c r="F201" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
       <c r="G201" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
       <c r="H201" t="s">
         <v>44</v>
@@ -17999,7 +18004,7 @@
         <v>677</v>
       </c>
       <c r="K201" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.2">
@@ -18007,22 +18012,22 @@
         <v>302</v>
       </c>
       <c r="B202" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C202" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
       <c r="D202" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E202" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
       <c r="F202" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
       <c r="G202" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
       <c r="H202" t="s">
         <v>44</v>
@@ -18034,7 +18039,7 @@
         <v>677</v>
       </c>
       <c r="K202" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.2">
@@ -18042,22 +18047,22 @@
         <v>303</v>
       </c>
       <c r="B203" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C203" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
       <c r="D203" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
       <c r="E203" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
       <c r="F203" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="G203" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
       <c r="H203" t="s">
         <v>44</v>
@@ -18069,7 +18074,7 @@
         <v>677</v>
       </c>
       <c r="K203" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.2">
@@ -18077,22 +18082,22 @@
         <v>304</v>
       </c>
       <c r="B204" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C204" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
       <c r="D204" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="E204" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="F204" t="s">
         <v>853</v>
       </c>
       <c r="G204" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="H204" t="s">
         <v>44</v>
@@ -18104,7 +18109,7 @@
         <v>677</v>
       </c>
       <c r="K204" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.2">
@@ -18112,22 +18117,22 @@
         <v>305</v>
       </c>
       <c r="B205" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C205" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="D205" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="E205" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
       <c r="F205" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
       <c r="G205" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H205" t="s">
         <v>703</v>
@@ -18139,7 +18144,7 @@
         <v>677</v>
       </c>
       <c r="K205" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.2">
@@ -18147,22 +18152,22 @@
         <v>306</v>
       </c>
       <c r="B206" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C206" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="D206" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="E206" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="F206" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="G206" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H206" t="s">
         <v>703</v>
@@ -18174,7 +18179,7 @@
         <v>677</v>
       </c>
       <c r="K206" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.2">
@@ -18182,22 +18187,22 @@
         <v>307</v>
       </c>
       <c r="B207" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C207" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="D207" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E207" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="F207" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="G207" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H207" t="s">
         <v>703</v>
@@ -18209,7 +18214,7 @@
         <v>677</v>
       </c>
       <c r="K207" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.2">
@@ -18217,22 +18222,22 @@
         <v>308</v>
       </c>
       <c r="B208" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C208" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="D208" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="E208" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="F208" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="G208" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
       <c r="H208" t="s">
         <v>44</v>
@@ -18244,7 +18249,7 @@
         <v>677</v>
       </c>
       <c r="K208" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.2">
@@ -18252,22 +18257,22 @@
         <v>309</v>
       </c>
       <c r="B209" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C209" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="D209" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="E209" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="F209" t="s">
         <v>1144</v>
       </c>
       <c r="G209" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H209" t="s">
         <v>703</v>
@@ -18279,7 +18284,7 @@
         <v>677</v>
       </c>
       <c r="K209" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.2">
@@ -18287,22 +18292,22 @@
         <v>310</v>
       </c>
       <c r="B210" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C210" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="D210" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="E210" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="F210" t="s">
         <v>1148</v>
       </c>
       <c r="G210" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H210" t="s">
         <v>703</v>
@@ -18314,7 +18319,7 @@
         <v>677</v>
       </c>
       <c r="K210" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.2">
@@ -18322,22 +18327,22 @@
         <v>311</v>
       </c>
       <c r="B211" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C211" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="D211" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E211" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F211" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="G211" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H211" t="s">
         <v>703</v>
@@ -18349,7 +18354,7 @@
         <v>677</v>
       </c>
       <c r="K211" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.2">
@@ -18357,22 +18362,22 @@
         <v>312</v>
       </c>
       <c r="B212" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="C212" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="D212" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="E212" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="F212" t="s">
         <v>824</v>
       </c>
       <c r="G212" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="H212" t="s">
         <v>703</v>
@@ -18384,7 +18389,7 @@
         <v>677</v>
       </c>
       <c r="K212" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.2">
@@ -18392,34 +18397,34 @@
         <v>313</v>
       </c>
       <c r="B213" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C213" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="D213" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="E213" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="F213" t="s">
         <v>757</v>
       </c>
       <c r="G213" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="H213" t="s">
         <v>44</v>
       </c>
       <c r="I213" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J213" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K213" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.2">
@@ -18427,16 +18432,16 @@
         <v>314</v>
       </c>
       <c r="B214" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C214" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="D214" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="E214" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="F214" t="s">
         <v>1043</v>
@@ -18448,10 +18453,10 @@
         <v>44</v>
       </c>
       <c r="I214" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J214" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K214" t="s">
         <v>1044</v>
@@ -18462,34 +18467,34 @@
         <v>315</v>
       </c>
       <c r="B215" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C215" t="s">
         <v>1591</v>
       </c>
-      <c r="C215" t="s">
-        <v>1599</v>
-      </c>
       <c r="D215" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="E215" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="F215" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="G215" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="H215" t="s">
         <v>44</v>
       </c>
       <c r="I215" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J215" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K215" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.2">
@@ -18497,34 +18502,34 @@
         <v>316</v>
       </c>
       <c r="B216" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C216" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="D216" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="E216" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="F216" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="G216" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="H216" t="s">
         <v>44</v>
       </c>
       <c r="I216" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J216" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K216" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.2">
@@ -18532,34 +18537,34 @@
         <v>317</v>
       </c>
       <c r="B217" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C217" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="D217" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="E217" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="F217" t="s">
         <v>853</v>
       </c>
       <c r="G217" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="H217" t="s">
         <v>44</v>
       </c>
       <c r="I217" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J217" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K217" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.2">
@@ -18567,34 +18572,34 @@
         <v>318</v>
       </c>
       <c r="B218" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C218" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="D218" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="E218" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="F218" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="G218" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H218" t="s">
         <v>703</v>
       </c>
       <c r="I218" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J218" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K218" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.2">
@@ -18602,34 +18607,34 @@
         <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C219" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="D219" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="E219" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="F219" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="G219" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H219" t="s">
         <v>703</v>
       </c>
       <c r="I219" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J219" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K219" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.2">
@@ -18637,34 +18642,34 @@
         <v>320</v>
       </c>
       <c r="B220" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C220" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="D220" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="E220" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="F220" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="G220" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="H220" t="s">
         <v>44</v>
       </c>
       <c r="I220" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J220" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K220" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.2">
@@ -18672,34 +18677,34 @@
         <v>321</v>
       </c>
       <c r="B221" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C221" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="D221" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="E221" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="F221" t="s">
         <v>875</v>
       </c>
       <c r="G221" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="H221" t="s">
         <v>44</v>
       </c>
       <c r="I221" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J221" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K221" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.2">
@@ -18707,34 +18712,34 @@
         <v>322</v>
       </c>
       <c r="B222" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C222" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="D222" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="E222" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="F222" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="G222" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H222" t="s">
         <v>703</v>
       </c>
       <c r="I222" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J222" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K222" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.2">
@@ -18742,34 +18747,34 @@
         <v>323</v>
       </c>
       <c r="B223" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C223" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="D223" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="E223" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="F223" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="G223" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H223" t="s">
         <v>703</v>
       </c>
       <c r="I223" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J223" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K223" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.2">
@@ -18777,34 +18782,34 @@
         <v>324</v>
       </c>
       <c r="B224" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C224" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="D224" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="E224" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="F224" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="G224" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H224" t="s">
         <v>703</v>
       </c>
       <c r="I224" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J224" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K224" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.2">
@@ -18812,34 +18817,34 @@
         <v>325</v>
       </c>
       <c r="B225" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C225" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
       <c r="D225" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="E225" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="F225" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
       <c r="G225" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H225" t="s">
         <v>703</v>
       </c>
       <c r="I225" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J225" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K225" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.2">
@@ -18847,34 +18852,34 @@
         <v>326</v>
       </c>
       <c r="B226" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C226" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="D226" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="E226" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="F226" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="G226" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H226" t="s">
         <v>703</v>
       </c>
       <c r="I226" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J226" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K226" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.2">
@@ -18882,34 +18887,34 @@
         <v>327</v>
       </c>
       <c r="B227" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="C227" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="D227" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="E227" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
       <c r="F227" t="s">
         <v>824</v>
       </c>
       <c r="G227" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="H227" t="s">
         <v>703</v>
       </c>
       <c r="I227" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J227" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K227" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.2">
@@ -18917,22 +18922,22 @@
         <v>328</v>
       </c>
       <c r="B228" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C228" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="D228" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="E228" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="F228" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="G228" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
       <c r="H228" t="s">
         <v>44</v>
@@ -18944,7 +18949,7 @@
         <v>1039</v>
       </c>
       <c r="K228" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.2">
@@ -18952,22 +18957,22 @@
         <v>329</v>
       </c>
       <c r="B229" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E229" t="s">
         <v>1652</v>
       </c>
-      <c r="C229" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D229" t="s">
-        <v>1659</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1660</v>
-      </c>
       <c r="F229" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
       <c r="G229" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="H229" t="s">
         <v>44</v>
@@ -18979,7 +18984,7 @@
         <v>1039</v>
       </c>
       <c r="K229" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.2">
@@ -18987,22 +18992,22 @@
         <v>330</v>
       </c>
       <c r="B230" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C230" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="D230" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="E230" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="F230" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="G230" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="H230" t="s">
         <v>44</v>
@@ -19014,7 +19019,7 @@
         <v>1039</v>
       </c>
       <c r="K230" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.2">
@@ -19022,22 +19027,22 @@
         <v>331</v>
       </c>
       <c r="B231" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C231" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="D231" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
       <c r="E231" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
       <c r="F231" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="G231" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
       <c r="H231" t="s">
         <v>44</v>
@@ -19049,7 +19054,7 @@
         <v>1039</v>
       </c>
       <c r="K231" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.2">
@@ -19057,22 +19062,22 @@
         <v>332</v>
       </c>
       <c r="B232" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C232" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
       <c r="D232" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="E232" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
       <c r="F232" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
       <c r="G232" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="H232" t="s">
         <v>44</v>
@@ -19084,7 +19089,7 @@
         <v>1039</v>
       </c>
       <c r="K232" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.2">
@@ -19092,22 +19097,22 @@
         <v>333</v>
       </c>
       <c r="B233" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C233" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
       <c r="D233" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
       <c r="E233" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
       <c r="F233" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
       <c r="G233" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H233" t="s">
         <v>703</v>
@@ -19119,7 +19124,7 @@
         <v>1039</v>
       </c>
       <c r="K233" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.2">
@@ -19127,22 +19132,22 @@
         <v>334</v>
       </c>
       <c r="B234" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C234" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
       <c r="D234" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
       <c r="E234" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="F234" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
       <c r="G234" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H234" t="s">
         <v>703</v>
@@ -19154,7 +19159,7 @@
         <v>1039</v>
       </c>
       <c r="K234" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.2">
@@ -19162,22 +19167,22 @@
         <v>335</v>
       </c>
       <c r="B235" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C235" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="D235" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="E235" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="F235" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
       <c r="G235" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H235" t="s">
         <v>703</v>
@@ -19189,7 +19194,7 @@
         <v>1039</v>
       </c>
       <c r="K235" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.2">
@@ -19197,22 +19202,22 @@
         <v>336</v>
       </c>
       <c r="B236" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C236" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="D236" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="E236" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="F236" t="s">
         <v>1010</v>
       </c>
       <c r="G236" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="H236" t="s">
         <v>44</v>
@@ -19224,7 +19229,7 @@
         <v>1039</v>
       </c>
       <c r="K236" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.2">
@@ -19232,22 +19237,22 @@
         <v>337</v>
       </c>
       <c r="B237" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C237" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
       <c r="D237" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
       <c r="E237" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="F237" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
       <c r="G237" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H237" t="s">
         <v>703</v>
@@ -19259,7 +19264,7 @@
         <v>1039</v>
       </c>
       <c r="K237" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.2">
@@ -19267,22 +19272,22 @@
         <v>338</v>
       </c>
       <c r="B238" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C238" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
       <c r="D238" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="E238" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="F238" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
       <c r="G238" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H238" t="s">
         <v>703</v>
@@ -19294,7 +19299,7 @@
         <v>1039</v>
       </c>
       <c r="K238" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.2">
@@ -19302,22 +19307,22 @@
         <v>339</v>
       </c>
       <c r="B239" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C239" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
       <c r="D239" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="E239" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="F239" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="G239" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
       <c r="H239" t="s">
         <v>44</v>
@@ -19329,7 +19334,7 @@
         <v>1039</v>
       </c>
       <c r="K239" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.2">
@@ -19337,22 +19342,22 @@
         <v>340</v>
       </c>
       <c r="B240" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C240" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
       <c r="D240" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="E240" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="F240" t="s">
         <v>813</v>
       </c>
       <c r="G240" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H240" t="s">
         <v>703</v>
@@ -19364,7 +19369,7 @@
         <v>1039</v>
       </c>
       <c r="K240" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.2">
@@ -19372,22 +19377,22 @@
         <v>341</v>
       </c>
       <c r="B241" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C241" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
       <c r="D241" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
       <c r="E241" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="F241" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="G241" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H241" t="s">
         <v>703</v>
@@ -19399,7 +19404,7 @@
         <v>1039</v>
       </c>
       <c r="K241" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.2">
@@ -19407,22 +19412,22 @@
         <v>342</v>
       </c>
       <c r="B242" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="C242" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
       <c r="D242" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
       <c r="E242" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="F242" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
       <c r="G242" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="H242" t="s">
         <v>703</v>
@@ -19434,7 +19439,7 @@
         <v>1039</v>
       </c>
       <c r="K242" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.2">
@@ -19442,16 +19447,16 @@
         <v>343</v>
       </c>
       <c r="B243" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C243" t="s">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="D243" t="s">
-        <v>1721</v>
+        <v>1713</v>
       </c>
       <c r="E243" t="s">
-        <v>1722</v>
+        <v>1714</v>
       </c>
       <c r="F243" t="s">
         <v>744</v>
@@ -19477,16 +19482,16 @@
         <v>344</v>
       </c>
       <c r="B244" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C244" t="s">
-        <v>1723</v>
+        <v>1715</v>
       </c>
       <c r="D244" t="s">
-        <v>1724</v>
+        <v>1716</v>
       </c>
       <c r="E244" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
       <c r="F244" t="s">
         <v>1043</v>
@@ -19512,22 +19517,22 @@
         <v>345</v>
       </c>
       <c r="B245" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D245" t="s">
         <v>1719</v>
       </c>
-      <c r="C245" t="s">
-        <v>1726</v>
-      </c>
-      <c r="D245" t="s">
-        <v>1727</v>
-      </c>
       <c r="E245" t="s">
-        <v>1728</v>
+        <v>1720</v>
       </c>
       <c r="F245" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
       <c r="G245" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
       <c r="H245" t="s">
         <v>44</v>
@@ -19539,7 +19544,7 @@
         <v>1039</v>
       </c>
       <c r="K245" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.2">
@@ -19547,22 +19552,22 @@
         <v>346</v>
       </c>
       <c r="B246" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C246" t="s">
-        <v>1730</v>
+        <v>1722</v>
       </c>
       <c r="D246" t="s">
-        <v>1731</v>
+        <v>1723</v>
       </c>
       <c r="E246" t="s">
-        <v>1732</v>
+        <v>1724</v>
       </c>
       <c r="F246" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
       <c r="G246" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
       <c r="H246" t="s">
         <v>44</v>
@@ -19574,7 +19579,7 @@
         <v>1039</v>
       </c>
       <c r="K246" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.2">
@@ -19582,22 +19587,22 @@
         <v>347</v>
       </c>
       <c r="B247" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C247" t="s">
-        <v>1734</v>
+        <v>1726</v>
       </c>
       <c r="D247" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="E247" t="s">
-        <v>1736</v>
+        <v>1728</v>
       </c>
       <c r="F247" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
       <c r="G247" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
       <c r="H247" t="s">
         <v>44</v>
@@ -19609,7 +19614,7 @@
         <v>1039</v>
       </c>
       <c r="K247" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.2">
@@ -19617,22 +19622,22 @@
         <v>348</v>
       </c>
       <c r="B248" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C248" t="s">
-        <v>1738</v>
+        <v>1730</v>
       </c>
       <c r="D248" t="s">
-        <v>1739</v>
+        <v>1731</v>
       </c>
       <c r="E248" t="s">
-        <v>1740</v>
+        <v>1732</v>
       </c>
       <c r="F248" t="s">
-        <v>1741</v>
+        <v>1733</v>
       </c>
       <c r="G248" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H248" t="s">
         <v>703</v>
@@ -19644,7 +19649,7 @@
         <v>1039</v>
       </c>
       <c r="K248" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.2">
@@ -19652,22 +19657,22 @@
         <v>349</v>
       </c>
       <c r="B249" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C249" t="s">
-        <v>1743</v>
+        <v>1735</v>
       </c>
       <c r="D249" t="s">
-        <v>1744</v>
+        <v>1736</v>
       </c>
       <c r="E249" t="s">
-        <v>1745</v>
+        <v>1737</v>
       </c>
       <c r="F249" t="s">
-        <v>1741</v>
+        <v>1733</v>
       </c>
       <c r="G249" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H249" t="s">
         <v>703</v>
@@ -19679,7 +19684,7 @@
         <v>1039</v>
       </c>
       <c r="K249" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.2">
@@ -19687,22 +19692,22 @@
         <v>350</v>
       </c>
       <c r="B250" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C250" t="s">
-        <v>1746</v>
+        <v>1738</v>
       </c>
       <c r="D250" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
       <c r="E250" t="s">
-        <v>1748</v>
+        <v>1740</v>
       </c>
       <c r="F250" t="s">
-        <v>1749</v>
+        <v>1741</v>
       </c>
       <c r="G250" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H250" t="s">
         <v>703</v>
@@ -19714,7 +19719,7 @@
         <v>1039</v>
       </c>
       <c r="K250" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.2">
@@ -19722,22 +19727,22 @@
         <v>351</v>
       </c>
       <c r="B251" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C251" t="s">
-        <v>1750</v>
+        <v>1742</v>
       </c>
       <c r="D251" t="s">
-        <v>1751</v>
+        <v>1743</v>
       </c>
       <c r="E251" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
       <c r="F251" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
       <c r="G251" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
       <c r="H251" t="s">
         <v>44</v>
@@ -19749,7 +19754,7 @@
         <v>1039</v>
       </c>
       <c r="K251" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.2">
@@ -19757,22 +19762,22 @@
         <v>352</v>
       </c>
       <c r="B252" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C252" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
       <c r="D252" t="s">
-        <v>1755</v>
+        <v>1747</v>
       </c>
       <c r="E252" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="F252" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
       <c r="G252" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H252" t="s">
         <v>703</v>
@@ -19784,7 +19789,7 @@
         <v>1039</v>
       </c>
       <c r="K252" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.2">
@@ -19792,22 +19797,22 @@
         <v>353</v>
       </c>
       <c r="B253" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C253" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
       <c r="D253" t="s">
-        <v>1759</v>
+        <v>1751</v>
       </c>
       <c r="E253" t="s">
-        <v>1760</v>
+        <v>1752</v>
       </c>
       <c r="F253" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="G253" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H253" t="s">
         <v>703</v>
@@ -19819,7 +19824,7 @@
         <v>1039</v>
       </c>
       <c r="K253" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.2">
@@ -19827,22 +19832,22 @@
         <v>354</v>
       </c>
       <c r="B254" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C254" t="s">
-        <v>1762</v>
+        <v>1754</v>
       </c>
       <c r="D254" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
       <c r="E254" t="s">
-        <v>1764</v>
+        <v>1756</v>
       </c>
       <c r="F254" t="s">
         <v>813</v>
       </c>
       <c r="G254" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H254" t="s">
         <v>703</v>
@@ -19854,7 +19859,7 @@
         <v>1039</v>
       </c>
       <c r="K254" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.2">
@@ -19862,16 +19867,16 @@
         <v>355</v>
       </c>
       <c r="B255" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C255" t="s">
-        <v>1765</v>
+        <v>1757</v>
       </c>
       <c r="D255" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="E255" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
       <c r="F255" t="s">
         <v>1087</v>
@@ -19897,22 +19902,22 @@
         <v>356</v>
       </c>
       <c r="B256" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C256" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="D256" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
       <c r="E256" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
       <c r="F256" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
       <c r="G256" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H256" t="s">
         <v>703</v>
@@ -19924,7 +19929,7 @@
         <v>1039</v>
       </c>
       <c r="K256" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.2">
@@ -19932,22 +19937,22 @@
         <v>357</v>
       </c>
       <c r="B257" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C257" t="s">
-        <v>1772</v>
+        <v>1764</v>
       </c>
       <c r="D257" t="s">
-        <v>1773</v>
+        <v>1765</v>
       </c>
       <c r="E257" t="s">
-        <v>1774</v>
+        <v>1766</v>
       </c>
       <c r="F257" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
       <c r="G257" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H257" t="s">
         <v>703</v>
@@ -19959,7 +19964,7 @@
         <v>1039</v>
       </c>
       <c r="K257" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.2">
@@ -19967,22 +19972,22 @@
         <v>358</v>
       </c>
       <c r="B258" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C258" t="s">
-        <v>1776</v>
+        <v>1768</v>
       </c>
       <c r="D258" t="s">
-        <v>1777</v>
+        <v>1769</v>
       </c>
       <c r="E258" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
       <c r="F258" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
       <c r="G258" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H258" t="s">
         <v>703</v>
@@ -19994,7 +19999,7 @@
         <v>1039</v>
       </c>
       <c r="K258" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.2">
@@ -20002,22 +20007,22 @@
         <v>359</v>
       </c>
       <c r="B259" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C259" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
       <c r="D259" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
       <c r="E259" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
       <c r="F259" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
       <c r="G259" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H259" t="s">
         <v>703</v>
@@ -20029,7 +20034,7 @@
         <v>1039</v>
       </c>
       <c r="K259" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.2">
@@ -20037,22 +20042,22 @@
         <v>360</v>
       </c>
       <c r="B260" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="C260" t="s">
-        <v>1784</v>
+        <v>1776</v>
       </c>
       <c r="D260" t="s">
-        <v>1785</v>
+        <v>1777</v>
       </c>
       <c r="E260" t="s">
-        <v>1786</v>
+        <v>1778</v>
       </c>
       <c r="F260" t="s">
-        <v>1787</v>
+        <v>1779</v>
       </c>
       <c r="G260" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="H260" t="s">
         <v>703</v>
@@ -20064,7 +20069,7 @@
         <v>1039</v>
       </c>
       <c r="K260" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.2">
@@ -20072,16 +20077,16 @@
         <v>361</v>
       </c>
       <c r="B261" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C261" t="s">
-        <v>1789</v>
+        <v>1781</v>
       </c>
       <c r="D261" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
       <c r="E261" t="s">
-        <v>1791</v>
+        <v>1783</v>
       </c>
       <c r="F261" t="s">
         <v>757</v>
@@ -20107,22 +20112,22 @@
         <v>362</v>
       </c>
       <c r="B262" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C262" t="s">
-        <v>1792</v>
+        <v>1784</v>
       </c>
       <c r="D262" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="E262" t="s">
-        <v>1794</v>
+        <v>1786</v>
       </c>
       <c r="F262" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
       <c r="G262" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
       <c r="H262" t="s">
         <v>44</v>
@@ -20134,7 +20139,7 @@
         <v>1039</v>
       </c>
       <c r="K262" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.2">
@@ -20142,22 +20147,22 @@
         <v>363</v>
       </c>
       <c r="B263" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C263" t="s">
         <v>1788</v>
       </c>
-      <c r="C263" t="s">
-        <v>1796</v>
-      </c>
       <c r="D263" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
       <c r="E263" t="s">
-        <v>1798</v>
+        <v>1790</v>
       </c>
       <c r="F263" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
       <c r="G263" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
       <c r="H263" t="s">
         <v>44</v>
@@ -20169,7 +20174,7 @@
         <v>1039</v>
       </c>
       <c r="K263" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.2">
@@ -20177,22 +20182,22 @@
         <v>364</v>
       </c>
       <c r="B264" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C264" t="s">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="D264" t="s">
-        <v>1801</v>
+        <v>1793</v>
       </c>
       <c r="E264" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
       <c r="F264" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
       <c r="G264" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
       <c r="H264" t="s">
         <v>44</v>
@@ -20204,7 +20209,7 @@
         <v>1039</v>
       </c>
       <c r="K264" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.2">
@@ -20212,22 +20217,22 @@
         <v>365</v>
       </c>
       <c r="B265" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C265" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
       <c r="D265" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="E265" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
       <c r="F265" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
       <c r="G265" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
       <c r="H265" t="s">
         <v>44</v>
@@ -20239,7 +20244,7 @@
         <v>1039</v>
       </c>
       <c r="K265" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.2">
@@ -20247,22 +20252,22 @@
         <v>366</v>
       </c>
       <c r="B266" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C266" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="D266" t="s">
-        <v>1809</v>
+        <v>1801</v>
       </c>
       <c r="E266" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
       <c r="F266" t="s">
-        <v>1811</v>
+        <v>1803</v>
       </c>
       <c r="G266" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H266" t="s">
         <v>703</v>
@@ -20274,7 +20279,7 @@
         <v>1039</v>
       </c>
       <c r="K266" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.2">
@@ -20282,22 +20287,22 @@
         <v>367</v>
       </c>
       <c r="B267" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C267" t="s">
-        <v>1813</v>
+        <v>1805</v>
       </c>
       <c r="D267" t="s">
-        <v>1814</v>
+        <v>1806</v>
       </c>
       <c r="E267" t="s">
-        <v>1815</v>
+        <v>1807</v>
       </c>
       <c r="F267" t="s">
-        <v>1816</v>
+        <v>1808</v>
       </c>
       <c r="G267" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H267" t="s">
         <v>703</v>
@@ -20309,7 +20314,7 @@
         <v>1039</v>
       </c>
       <c r="K267" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.2">
@@ -20317,22 +20322,22 @@
         <v>368</v>
       </c>
       <c r="B268" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C268" t="s">
-        <v>1817</v>
+        <v>1809</v>
       </c>
       <c r="D268" t="s">
-        <v>1818</v>
+        <v>1810</v>
       </c>
       <c r="E268" t="s">
-        <v>1819</v>
+        <v>1811</v>
       </c>
       <c r="F268" t="s">
-        <v>1820</v>
+        <v>1812</v>
       </c>
       <c r="G268" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H268" t="s">
         <v>703</v>
@@ -20344,7 +20349,7 @@
         <v>1039</v>
       </c>
       <c r="K268" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.2">
@@ -20352,22 +20357,22 @@
         <v>369</v>
       </c>
       <c r="B269" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C269" t="s">
-        <v>1821</v>
+        <v>1813</v>
       </c>
       <c r="D269" t="s">
-        <v>1822</v>
+        <v>1814</v>
       </c>
       <c r="E269" t="s">
-        <v>1823</v>
+        <v>1815</v>
       </c>
       <c r="F269" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="G269" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="H269" t="s">
         <v>44</v>
@@ -20379,7 +20384,7 @@
         <v>1039</v>
       </c>
       <c r="K269" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.2">
@@ -20387,22 +20392,22 @@
         <v>370</v>
       </c>
       <c r="B270" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C270" t="s">
-        <v>1825</v>
+        <v>1817</v>
       </c>
       <c r="D270" t="s">
-        <v>1826</v>
+        <v>1818</v>
       </c>
       <c r="E270" t="s">
-        <v>1827</v>
+        <v>1819</v>
       </c>
       <c r="F270" t="s">
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="G270" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H270" t="s">
         <v>703</v>
@@ -20414,7 +20419,7 @@
         <v>1039</v>
       </c>
       <c r="K270" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.2">
@@ -20422,22 +20427,22 @@
         <v>371</v>
       </c>
       <c r="B271" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C271" t="s">
-        <v>1829</v>
+        <v>1821</v>
       </c>
       <c r="D271" t="s">
-        <v>1830</v>
+        <v>1822</v>
       </c>
       <c r="E271" t="s">
-        <v>1831</v>
+        <v>1823</v>
       </c>
       <c r="F271" t="s">
-        <v>1832</v>
+        <v>1824</v>
       </c>
       <c r="G271" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H271" t="s">
         <v>703</v>
@@ -20449,7 +20454,7 @@
         <v>1039</v>
       </c>
       <c r="K271" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.2">
@@ -20457,22 +20462,22 @@
         <v>372</v>
       </c>
       <c r="B272" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C272" t="s">
-        <v>1833</v>
+        <v>1825</v>
       </c>
       <c r="D272" t="s">
-        <v>1834</v>
+        <v>1826</v>
       </c>
       <c r="E272" t="s">
-        <v>1835</v>
+        <v>1827</v>
       </c>
       <c r="F272" t="s">
         <v>813</v>
       </c>
       <c r="G272" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H272" t="s">
         <v>703</v>
@@ -20484,7 +20489,7 @@
         <v>1039</v>
       </c>
       <c r="K272" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
@@ -20492,22 +20497,22 @@
         <v>373</v>
       </c>
       <c r="B273" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C273" t="s">
-        <v>1836</v>
+        <v>1828</v>
       </c>
       <c r="D273" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="E273" t="s">
-        <v>1838</v>
+        <v>1830</v>
       </c>
       <c r="F273" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
       <c r="G273" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
       <c r="H273" t="s">
         <v>44</v>
@@ -20519,7 +20524,7 @@
         <v>1039</v>
       </c>
       <c r="K273" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
@@ -20527,22 +20532,22 @@
         <v>374</v>
       </c>
       <c r="B274" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C274" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="D274" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="E274" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
       <c r="F274" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
       <c r="G274" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H274" t="s">
         <v>703</v>
@@ -20554,7 +20559,7 @@
         <v>1039</v>
       </c>
       <c r="K274" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
@@ -20562,22 +20567,22 @@
         <v>375</v>
       </c>
       <c r="B275" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C275" t="s">
-        <v>1843</v>
+        <v>1835</v>
       </c>
       <c r="D275" t="s">
-        <v>1844</v>
+        <v>1836</v>
       </c>
       <c r="E275" t="s">
-        <v>1845</v>
+        <v>1837</v>
       </c>
       <c r="F275" t="s">
-        <v>1846</v>
+        <v>1838</v>
       </c>
       <c r="G275" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H275" t="s">
         <v>703</v>
@@ -20589,7 +20594,7 @@
         <v>1039</v>
       </c>
       <c r="K275" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
@@ -20597,22 +20602,22 @@
         <v>376</v>
       </c>
       <c r="B276" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C276" t="s">
-        <v>1847</v>
+        <v>1839</v>
       </c>
       <c r="D276" t="s">
-        <v>1848</v>
+        <v>1840</v>
       </c>
       <c r="E276" t="s">
-        <v>1849</v>
+        <v>1841</v>
       </c>
       <c r="F276" t="s">
         <v>744</v>
       </c>
       <c r="G276" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H276" t="s">
         <v>703</v>
@@ -20624,7 +20629,7 @@
         <v>1039</v>
       </c>
       <c r="K276" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
@@ -20632,22 +20637,22 @@
         <v>377</v>
       </c>
       <c r="B277" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C277" t="s">
-        <v>1850</v>
+        <v>1842</v>
       </c>
       <c r="D277" t="s">
-        <v>1851</v>
+        <v>1843</v>
       </c>
       <c r="E277" t="s">
-        <v>1852</v>
+        <v>1844</v>
       </c>
       <c r="F277" t="s">
-        <v>1853</v>
+        <v>1845</v>
       </c>
       <c r="G277" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H277" t="s">
         <v>703</v>
@@ -20659,7 +20664,7 @@
         <v>1039</v>
       </c>
       <c r="K277" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
@@ -20667,22 +20672,22 @@
         <v>378</v>
       </c>
       <c r="B278" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="C278" t="s">
-        <v>1854</v>
+        <v>1846</v>
       </c>
       <c r="D278" t="s">
-        <v>1855</v>
+        <v>1847</v>
       </c>
       <c r="E278" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
       <c r="F278" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
       <c r="G278" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
       <c r="H278" t="s">
         <v>703</v>
@@ -20694,10 +20699,53 @@
         <v>1039</v>
       </c>
       <c r="K278" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J128" r:id="rId1" xr:uid="{2595DC30-8EAD-A242-929C-52B76D636513}"/>
+    <hyperlink ref="J129" r:id="rId2" xr:uid="{EE26B384-A21A-BA4B-AC6D-5CE7B453ADCD}"/>
+    <hyperlink ref="J130" r:id="rId3" xr:uid="{37E1FBEF-D432-2C44-9C05-8C928514689D}"/>
+    <hyperlink ref="J131" r:id="rId4" xr:uid="{DFA0E732-C67A-6B4A-ADB7-301E8983A48E}"/>
+    <hyperlink ref="J132" r:id="rId5" xr:uid="{6CD13686-6FAF-E640-B3FE-CA9824ECE133}"/>
+    <hyperlink ref="J133" r:id="rId6" xr:uid="{1D23A2E0-5A25-DF45-8EAC-428A45902D22}"/>
+    <hyperlink ref="J134" r:id="rId7" xr:uid="{E442C6F0-CBFC-EB40-8EF4-FA8E65AA5B26}"/>
+    <hyperlink ref="J135" r:id="rId8" xr:uid="{356D83EF-82BF-204B-A590-F73A7074AB1C}"/>
+    <hyperlink ref="J136" r:id="rId9" xr:uid="{D3D49241-1DEE-E941-89F6-406780C226AE}"/>
+    <hyperlink ref="J137" r:id="rId10" xr:uid="{78BC0C76-75AE-4F4D-9332-0541074523C4}"/>
+    <hyperlink ref="J138" r:id="rId11" xr:uid="{E8F4385E-18B6-BD40-9D19-35609E9C2648}"/>
+    <hyperlink ref="J139" r:id="rId12" xr:uid="{0414D48F-D9EE-0E48-A12C-7A91AD6B8763}"/>
+    <hyperlink ref="J140" r:id="rId13" xr:uid="{D1FE84D6-0A04-CE48-907D-78C2CD1F0040}"/>
+    <hyperlink ref="J141" r:id="rId14" xr:uid="{4D88DEC6-D488-4C49-A6B0-C5450B96A348}"/>
+    <hyperlink ref="J142" r:id="rId15" xr:uid="{7B55386B-8BCD-8C4D-B968-7142B78151A3}"/>
+    <hyperlink ref="J143" r:id="rId16" xr:uid="{769F5C74-7B8A-AE46-B066-69660465D53D}"/>
+    <hyperlink ref="J144" r:id="rId17" xr:uid="{2B54FDB3-F022-6248-AF0E-2EE698899D3C}"/>
+    <hyperlink ref="J145" r:id="rId18" xr:uid="{1698ED23-979B-8E45-A942-65E3013EA702}"/>
+    <hyperlink ref="J146" r:id="rId19" xr:uid="{B2771C9A-460A-0648-93EF-83A09C29D3A4}"/>
+    <hyperlink ref="J147" r:id="rId20" xr:uid="{6ADD1DFA-28FC-6345-A95B-EA76F9DCF7A7}"/>
+    <hyperlink ref="J148" r:id="rId21" xr:uid="{0EF133AF-6B59-6946-84A2-D161110788F1}"/>
+    <hyperlink ref="J149" r:id="rId22" xr:uid="{13A0227A-3946-7F40-847C-0A7C15786476}"/>
+    <hyperlink ref="J150" r:id="rId23" xr:uid="{04C06A5F-D91D-174B-A226-B705E879A59E}"/>
+    <hyperlink ref="J151" r:id="rId24" xr:uid="{F6B36DCB-DC5B-3749-9A3B-A86CDA2AD846}"/>
+    <hyperlink ref="J152" r:id="rId25" xr:uid="{EB1BA338-C50A-7D4C-9392-26BCE89425C0}"/>
+    <hyperlink ref="J153" r:id="rId26" xr:uid="{F57146DF-7893-204D-A576-5582B7CA78B2}"/>
+    <hyperlink ref="J154" r:id="rId27" xr:uid="{E50778BD-71FD-8346-840D-F38532D6CB42}"/>
+    <hyperlink ref="J155" r:id="rId28" xr:uid="{F61B9D65-2D7B-9B4C-A708-FF8E512E83E4}"/>
+    <hyperlink ref="J156" r:id="rId29" xr:uid="{3083976B-A517-A947-A331-A085CBC5AD8D}"/>
+    <hyperlink ref="J157" r:id="rId30" xr:uid="{0F25C586-8754-4841-9BD9-5DB2D9FAE997}"/>
+    <hyperlink ref="J158" r:id="rId31" xr:uid="{716D1FFD-E173-D648-B58F-2B6E19349F79}"/>
+    <hyperlink ref="J159" r:id="rId32" xr:uid="{C3C2B3CC-4936-E942-8411-9273BC4BA23F}"/>
+    <hyperlink ref="J160" r:id="rId33" xr:uid="{5EB9151E-5C74-574B-82C8-E732D9250103}"/>
+    <hyperlink ref="J161" r:id="rId34" xr:uid="{AEC944ED-C9C9-6A40-B009-6CAB45DF29BA}"/>
+    <hyperlink ref="J162" r:id="rId35" xr:uid="{F1A0ABE7-FB4C-3940-A7EC-FB9703E48DCB}"/>
+    <hyperlink ref="J163" r:id="rId36" xr:uid="{17A65BC2-2FF3-5145-A5CD-1A6C98302216}"/>
+    <hyperlink ref="J164" r:id="rId37" xr:uid="{79D171F2-7988-4447-95BB-D7278A45E1C1}"/>
+    <hyperlink ref="J165" r:id="rId38" xr:uid="{F362817E-20FD-5D43-BD29-7C55D14EE12D}"/>
+    <hyperlink ref="J166" r:id="rId39" xr:uid="{8D0E61FD-7D53-014F-B132-5D48B97B5CCD}"/>
+    <hyperlink ref="J167" r:id="rId40" xr:uid="{8D74FDA2-FB34-0A4F-9BBF-CA01603C35F9}"/>
+    <hyperlink ref="J168" r:id="rId41" xr:uid="{E65B0AB5-DEFD-4F43-AC91-843D7DFC22F9}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20712,7 +20760,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -20723,7 +20771,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1859</v>
+        <v>1851</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -20734,18 +20782,18 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1860</v>
+        <v>1852</v>
       </c>
       <c r="B3" t="s">
-        <v>1905</v>
+        <v>1897</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1906</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
       <c r="B4" t="s">
         <v>902</v>
@@ -20756,40 +20804,40 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
       <c r="B5" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="C5" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
       <c r="B6" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="C6" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1864</v>
+        <v>1856</v>
       </c>
       <c r="B7" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="C7" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1865</v>
+        <v>1857</v>
       </c>
       <c r="B8" t="s">
         <v>676</v>
@@ -20800,7 +20848,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1866</v>
+        <v>1858</v>
       </c>
       <c r="B9" t="s">
         <v>676</v>
@@ -20811,7 +20859,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1867</v>
+        <v>1859</v>
       </c>
       <c r="B10" t="s">
         <v>676</v>
@@ -20822,7 +20870,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1868</v>
+        <v>1860</v>
       </c>
       <c r="B11" t="s">
         <v>676</v>
@@ -20833,7 +20881,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1869</v>
+        <v>1861</v>
       </c>
       <c r="B12" t="s">
         <v>676</v>
@@ -20844,7 +20892,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1870</v>
+        <v>1862</v>
       </c>
       <c r="B13" t="s">
         <v>1038</v>
@@ -20855,7 +20903,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1871</v>
+        <v>1863</v>
       </c>
       <c r="B14" t="s">
         <v>1038</v>
@@ -20866,7 +20914,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1872</v>
+        <v>1864</v>
       </c>
       <c r="B15" t="s">
         <v>1038</v>
@@ -20877,7 +20925,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1873</v>
+        <v>1865</v>
       </c>
       <c r="B16" t="s">
         <v>1038</v>
@@ -20888,7 +20936,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1874</v>
+        <v>1866</v>
       </c>
       <c r="B17" t="s">
         <v>1038</v>
@@ -20912,122 +20960,122 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1876</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="B3" t="s">
-        <v>1878</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1879</v>
+        <v>1871</v>
       </c>
       <c r="B4" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1881</v>
+        <v>1873</v>
       </c>
       <c r="B6" t="s">
-        <v>1882</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1883</v>
+        <v>1875</v>
       </c>
       <c r="B7" t="s">
-        <v>1884</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1885</v>
+        <v>1877</v>
       </c>
       <c r="B8" t="s">
-        <v>1886</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1887</v>
+        <v>1879</v>
       </c>
       <c r="B9" t="s">
-        <v>1888</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1889</v>
+        <v>1881</v>
       </c>
       <c r="B10" t="s">
-        <v>1890</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1891</v>
+        <v>1883</v>
       </c>
       <c r="B11" t="s">
-        <v>1892</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1893</v>
+        <v>1885</v>
       </c>
       <c r="B13" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1895</v>
+        <v>1887</v>
       </c>
       <c r="B14" t="s">
-        <v>1896</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1897</v>
+        <v>1889</v>
       </c>
       <c r="B15" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1899</v>
+        <v>1891</v>
       </c>
       <c r="B17" t="s">
-        <v>1900</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1901</v>
+        <v>1893</v>
       </c>
       <c r="B18" t="s">
-        <v>1902</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1903</v>
+        <v>1895</v>
       </c>
       <c r="B19" t="s">
-        <v>1904</v>
+        <v>1896</v>
       </c>
     </row>
   </sheetData>
